--- a/Fudbal Bezanija Golovi.xlsx
+++ b/Fudbal Bezanija Golovi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beoog\Desktop\Fudbal Bezanija\Raw Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beoog\Desktop\Fudbal Bezanija\Sajt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591E1C21-409D-4FE6-9646-AB7C2E061AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF48AEE-1EB2-41CE-88BD-9737D373670F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="47">
   <si>
     <t>NaN</t>
   </si>
@@ -176,25 +176,13 @@
   <si>
     <t>Body</t>
   </si>
-  <si>
-    <t>Лева нога</t>
-  </si>
-  <si>
-    <t>Десна нога</t>
-  </si>
-  <si>
-    <t>Глава</t>
-  </si>
-  <si>
-    <t>Тело</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -535,10 +523,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -10562,64 +10550,28 @@
       </c>
     </row>
     <row r="258" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D258" s="30"/>
-      <c r="E258" s="30"/>
+      <c r="D258" s="31"/>
+      <c r="E258" s="31"/>
     </row>
     <row r="259" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D259" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="E259" s="30"/>
-      <c r="F259" s="1">
-        <f>COUNTIF(G2:G256, "Left Foot")</f>
-        <v>31</v>
-      </c>
-      <c r="G259" s="31">
-        <f>F259*100/255</f>
-        <v>12.156862745098039</v>
-      </c>
+      <c r="D259" s="31"/>
+      <c r="E259" s="31"/>
+      <c r="G259" s="30"/>
     </row>
     <row r="260" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D260" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E260" s="30"/>
-      <c r="F260" s="1">
-        <f>COUNTIF(G2:G256, "Right Foot")</f>
-        <v>218</v>
-      </c>
-      <c r="G260" s="31">
-        <f t="shared" ref="G260:G262" si="37">F260*100/255</f>
-        <v>85.490196078431367</v>
-      </c>
+      <c r="D260" s="31"/>
+      <c r="E260" s="31"/>
+      <c r="G260" s="30"/>
     </row>
     <row r="261" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D261" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="E261" s="30"/>
-      <c r="F261" s="1">
-        <f>COUNTIF(G2:G256,"Header")</f>
-        <v>5</v>
-      </c>
-      <c r="G261" s="31">
-        <f t="shared" si="37"/>
-        <v>1.9607843137254901</v>
-      </c>
+      <c r="D261" s="31"/>
+      <c r="E261" s="31"/>
+      <c r="G261" s="30"/>
     </row>
     <row r="262" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D262" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="E262" s="30"/>
-      <c r="F262" s="1">
-        <f>COUNTIF(G2:G256, "Body")</f>
-        <v>1</v>
-      </c>
-      <c r="G262" s="31">
-        <f t="shared" si="37"/>
-        <v>0.39215686274509803</v>
-      </c>
+      <c r="D262" s="31"/>
+      <c r="E262" s="31"/>
+      <c r="G262" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Fudbal Bezanija Golovi.xlsx
+++ b/Fudbal Bezanija Golovi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beoog\Desktop\Fudbal Bezanija\Sajt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF48AEE-1EB2-41CE-88BD-9737D373670F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5105AA-89D5-4D6F-B577-8B2689286CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Golovi" sheetId="2" r:id="rId1"/>
@@ -10499,11 +10499,11 @@
         <v>54</v>
       </c>
       <c r="I255" s="2">
-        <f t="shared" ref="I255:I256" si="34">IF(C255="Black",I254+1,(IF(C255="Colored",I254+1,I254)))</f>
+        <f t="shared" ref="I255" si="34">IF(C255="Black",I254+1,(IF(C255="Colored",I254+1,I254)))</f>
         <v>3</v>
       </c>
       <c r="J255" s="2">
-        <f t="shared" ref="J255:J256" si="35">IF(C255="White",J254+1,(IF(C255="Bibs",J254+1,J254)))</f>
+        <f t="shared" ref="J255" si="35">IF(C255="White",J254+1,(IF(C255="Bibs",J254+1,J254)))</f>
         <v>9</v>
       </c>
       <c r="K255" s="4">
@@ -10537,11 +10537,11 @@
         <v>56</v>
       </c>
       <c r="I256" s="8">
-        <f t="shared" si="34"/>
+        <f>IF(C256="Black",I255+1,(IF(C256="Colored",I255+1,I255)))</f>
         <v>4</v>
       </c>
       <c r="J256" s="8">
-        <f t="shared" si="35"/>
+        <f>IF(C256="White",J255+1,(IF(C256="Bibs",J255+1,J255)))</f>
         <v>9</v>
       </c>
       <c r="K256" s="9">

--- a/Fudbal Bezanija Golovi.xlsx
+++ b/Fudbal Bezanija Golovi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beoog\Desktop\Fudbal Bezanija\Sajt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5105AA-89D5-4D6F-B577-8B2689286CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FCFED36-0291-4C8F-885D-0FFC6D703094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,9 +99,6 @@
     <t>Strahinja Milovanovic</t>
   </si>
   <si>
-    <t>Drug Tegijev Marko</t>
-  </si>
-  <si>
     <t>Ivan Filipovic</t>
   </si>
   <si>
@@ -175,6 +172,9 @@
   </si>
   <si>
     <t>Body</t>
+  </si>
+  <si>
+    <t>Nenad</t>
   </si>
 </sst>
 </file>
@@ -843,28 +843,28 @@
         <v>3</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="H1" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H2" s="3">
         <v>3</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H3" s="2">
         <v>5</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H4" s="2">
         <v>9</v>
@@ -999,7 +999,7 @@
         <v>17</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H5" s="2">
         <v>12</v>
@@ -1037,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H6" s="2">
         <v>15</v>
@@ -1075,7 +1075,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H7" s="2">
         <v>18</v>
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H8" s="2">
         <v>21</v>
@@ -1151,7 +1151,7 @@
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H9" s="2">
         <v>23</v>
@@ -1189,7 +1189,7 @@
         <v>16</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H10" s="2">
         <v>24</v>
@@ -1218,7 +1218,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>13</v>
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H11" s="2">
         <v>26</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H12" s="2">
         <v>27</v>
@@ -1303,7 +1303,7 @@
         <v>13</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H13" s="2">
         <v>28</v>
@@ -1341,7 +1341,7 @@
         <v>14</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H14" s="2">
         <v>35</v>
@@ -1379,7 +1379,7 @@
         <v>13</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H15" s="2">
         <v>39</v>
@@ -1417,7 +1417,7 @@
         <v>17</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H16" s="2">
         <v>41</v>
@@ -1446,7 +1446,7 @@
         <v>5</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" s="25" t="s">
         <v>11</v>
@@ -1455,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H17" s="2">
         <v>48</v>
@@ -1493,7 +1493,7 @@
         <v>9</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H18" s="2">
         <v>49</v>
@@ -1531,7 +1531,7 @@
         <v>9</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H19" s="2">
         <v>53</v>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H20" s="2">
         <v>59</v>
@@ -1607,7 +1607,7 @@
         <v>14</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2">
         <v>60</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H22" s="2">
         <v>65</v>
@@ -1683,7 +1683,7 @@
         <v>17</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H23" s="2">
         <v>3</v>
@@ -1719,7 +1719,7 @@
         <v>19</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H24" s="2">
         <v>13</v>
@@ -1757,7 +1757,7 @@
         <v>13</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H25" s="2">
         <v>14</v>
@@ -1795,7 +1795,7 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H26" s="2">
         <v>15</v>
@@ -1833,7 +1833,7 @@
         <v>10</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H27" s="2">
         <v>17</v>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H28" s="2">
         <v>18</v>
@@ -1909,7 +1909,7 @@
         <v>19</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H29" s="2">
         <v>19</v>
@@ -1947,7 +1947,7 @@
         <v>11</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H30" s="2">
         <v>22</v>
@@ -1985,7 +1985,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H31" s="2">
         <v>23</v>
@@ -2014,7 +2014,7 @@
         <v>4</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E32" s="25" t="s">
         <v>11</v>
@@ -2023,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H32" s="2">
         <v>25</v>
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H33" s="2">
         <v>26</v>
@@ -2099,7 +2099,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H34" s="2">
         <v>28</v>
@@ -2137,7 +2137,7 @@
         <v>13</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H35" s="2">
         <v>32</v>
@@ -2175,7 +2175,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H36" s="2">
         <v>34</v>
@@ -2213,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H37" s="2">
         <v>35</v>
@@ -2251,7 +2251,7 @@
         <v>13</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H38" s="2">
         <v>38</v>
@@ -2289,7 +2289,7 @@
         <v>9</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H39" s="2">
         <v>47</v>
@@ -2327,7 +2327,7 @@
         <v>9</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H40" s="2">
         <v>48</v>
@@ -2365,7 +2365,7 @@
         <v>8</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H41" s="2">
         <v>57</v>
@@ -2403,7 +2403,7 @@
         <v>17</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H42" s="2">
         <v>60</v>
@@ -2441,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H43" s="2">
         <v>65</v>
@@ -2470,16 +2470,16 @@
         <v>6</v>
       </c>
       <c r="D44" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E44" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E44" s="25" t="s">
-        <v>22</v>
-      </c>
       <c r="F44" s="19" t="s">
         <v>8</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H44" s="2">
         <v>2</v>
@@ -2506,16 +2506,16 @@
         <v>6</v>
       </c>
       <c r="D45" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E45" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E45" s="25" t="s">
-        <v>22</v>
-      </c>
       <c r="F45" s="19" t="s">
         <v>8</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H45" s="2">
         <v>4</v>
@@ -2553,7 +2553,7 @@
         <v>11</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H46" s="2">
         <v>6</v>
@@ -2582,7 +2582,7 @@
         <v>6</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="E47" s="25" t="s">
         <v>11</v>
@@ -2591,7 +2591,7 @@
         <v>8</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H47" s="2">
         <v>17</v>
@@ -2620,7 +2620,7 @@
         <v>7</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E48" s="25" t="s">
         <v>18</v>
@@ -2629,7 +2629,7 @@
         <v>11</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H48" s="2">
         <v>24</v>
@@ -2658,16 +2658,16 @@
         <v>6</v>
       </c>
       <c r="D49" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E49" s="25" t="s">
         <v>21</v>
-      </c>
-      <c r="E49" s="25" t="s">
-        <v>22</v>
       </c>
       <c r="F49" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H49" s="2">
         <v>26</v>
@@ -2705,7 +2705,7 @@
         <v>9</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H50" s="2">
         <v>27</v>
@@ -2734,7 +2734,7 @@
         <v>7</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E51" s="25" t="s">
         <v>9</v>
@@ -2743,7 +2743,7 @@
         <v>19</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H51" s="2">
         <v>34</v>
@@ -2781,7 +2781,7 @@
         <v>18</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H52" s="2">
         <v>36</v>
@@ -2816,10 +2816,10 @@
         <v>15</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H53" s="2">
         <v>39</v>
@@ -2848,7 +2848,7 @@
         <v>6</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="E54" s="25" t="s">
         <v>10</v>
@@ -2857,7 +2857,7 @@
         <v>18</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H54" s="2">
         <v>47</v>
@@ -2895,7 +2895,7 @@
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H55" s="2">
         <v>47</v>
@@ -2924,7 +2924,7 @@
         <v>6</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="E56" s="25" t="s">
         <v>11</v>
@@ -2933,7 +2933,7 @@
         <v>9</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H56" s="2">
         <v>47</v>
@@ -2962,7 +2962,7 @@
         <v>7</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E57" s="25" t="s">
         <v>9</v>
@@ -2971,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H57" s="2">
         <v>48</v>
@@ -3003,13 +3003,13 @@
         <v>8</v>
       </c>
       <c r="E58" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F58" s="19" t="s">
         <v>0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H58" s="2">
         <v>52</v>
@@ -3038,7 +3038,7 @@
         <v>7</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E59" s="25" t="s">
         <v>18</v>
@@ -3047,7 +3047,7 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H59" s="2">
         <v>53</v>
@@ -3076,16 +3076,16 @@
         <v>7</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E60" s="25" t="s">
         <v>18</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H60" s="2">
         <v>54</v>
@@ -3114,7 +3114,7 @@
         <v>6</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="E61" s="25" t="s">
         <v>11</v>
@@ -3123,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H61" s="2">
         <v>55</v>
@@ -3161,7 +3161,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H62" s="2">
         <v>56</v>
@@ -3196,10 +3196,10 @@
         <v>18</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H63" s="2">
         <v>58</v>
@@ -3228,7 +3228,7 @@
         <v>7</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E64" s="25" t="s">
         <v>18</v>
@@ -3237,7 +3237,7 @@
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H64" s="2">
         <v>68</v>
@@ -3275,7 +3275,7 @@
         <v>15</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H65" s="2">
         <v>69</v>
@@ -3304,16 +3304,16 @@
         <v>7</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E66" s="25" t="s">
         <v>18</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H66" s="2">
         <v>70</v>
@@ -3345,13 +3345,13 @@
         <v>12</v>
       </c>
       <c r="E67" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F67" s="19" t="s">
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H67" s="2">
         <v>15</v>
@@ -3384,10 +3384,10 @@
         <v>19</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H68" s="2">
         <v>15</v>
@@ -3416,16 +3416,16 @@
         <v>4</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E69" s="25" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F69" s="19" t="s">
         <v>19</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H69" s="2">
         <v>18</v>
@@ -3463,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H70" s="2">
         <v>20</v>
@@ -3495,13 +3495,13 @@
         <v>10</v>
       </c>
       <c r="E71" s="25" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F71" s="19" t="s">
         <v>19</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H71" s="2">
         <v>23</v>
@@ -3539,7 +3539,7 @@
         <v>8</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H72" s="2">
         <v>26</v>
@@ -3568,16 +3568,16 @@
         <v>5</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E73" s="25" t="s">
         <v>12</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H73" s="2">
         <v>28</v>
@@ -3606,16 +3606,16 @@
         <v>4</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E74" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F74" s="19" t="s">
         <v>0</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H74" s="2">
         <v>32</v>
@@ -3647,13 +3647,13 @@
         <v>10</v>
       </c>
       <c r="E75" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F75" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F75" s="19" t="s">
-        <v>23</v>
-      </c>
       <c r="G75" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H75" s="2">
         <v>38</v>
@@ -3691,7 +3691,7 @@
         <v>8</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H76" s="2">
         <v>39</v>
@@ -3729,7 +3729,7 @@
         <v>12</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H77" s="2">
         <v>40</v>
@@ -3767,7 +3767,7 @@
         <v>8</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H78" s="2">
         <v>43</v>
@@ -3805,7 +3805,7 @@
         <v>8</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H79" s="2">
         <v>45</v>
@@ -3843,7 +3843,7 @@
         <v>18</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H80" s="2">
         <v>49</v>
@@ -3872,7 +3872,7 @@
         <v>4</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E81" s="25" t="s">
         <v>8</v>
@@ -3881,7 +3881,7 @@
         <v>19</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H81" s="2">
         <v>50</v>
@@ -3919,7 +3919,7 @@
         <v>8</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H82" s="2">
         <v>51</v>
@@ -3957,7 +3957,7 @@
         <v>8</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H83" s="2">
         <v>53</v>
@@ -3992,10 +3992,10 @@
         <v>12</v>
       </c>
       <c r="F84" s="19" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H84" s="2">
         <v>6</v>
@@ -4031,7 +4031,7 @@
         <v>9</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H85" s="2">
         <v>15</v>
@@ -4069,7 +4069,7 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H86" s="2">
         <v>15</v>
@@ -4107,7 +4107,7 @@
         <v>9</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H87" s="2">
         <v>16</v>
@@ -4139,13 +4139,13 @@
         <v>19</v>
       </c>
       <c r="E88" s="25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F88" s="19" t="s">
         <v>18</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H88" s="2">
         <v>21</v>
@@ -4180,10 +4180,10 @@
         <v>18</v>
       </c>
       <c r="F89" s="19" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H89" s="2">
         <v>22</v>
@@ -4218,10 +4218,10 @@
         <v>16</v>
       </c>
       <c r="F90" s="19" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H90" s="2">
         <v>24</v>
@@ -4259,7 +4259,7 @@
         <v>17</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H91" s="2">
         <v>28</v>
@@ -4297,7 +4297,7 @@
         <v>19</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H92" s="2">
         <v>30</v>
@@ -4335,7 +4335,7 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H93" s="2">
         <v>33</v>
@@ -4373,7 +4373,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H94" s="2">
         <v>36</v>
@@ -4411,7 +4411,7 @@
         <v>18</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H95" s="2">
         <v>43</v>
@@ -4446,10 +4446,10 @@
         <v>10</v>
       </c>
       <c r="F96" s="19" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H96" s="2">
         <v>47</v>
@@ -4487,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H97" s="2">
         <v>49</v>
@@ -4516,7 +4516,7 @@
         <v>7</v>
       </c>
       <c r="D98" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E98" s="25" t="s">
         <v>10</v>
@@ -4525,7 +4525,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H98" s="2">
         <v>50</v>
@@ -4557,13 +4557,13 @@
         <v>16</v>
       </c>
       <c r="E99" s="25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F99" s="19" t="s">
         <v>0</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H99" s="2">
         <v>53</v>
@@ -4595,13 +4595,13 @@
         <v>16</v>
       </c>
       <c r="E100" s="25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F100" s="19" t="s">
         <v>12</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H100" s="2">
         <v>54</v>
@@ -4639,7 +4639,7 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H101" s="2">
         <v>58</v>
@@ -4677,7 +4677,7 @@
         <v>19</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H102" s="2">
         <v>58</v>
@@ -4715,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H103" s="2">
         <v>59</v>
@@ -4753,7 +4753,7 @@
         <v>9</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H104" s="2">
         <v>60</v>
@@ -4785,13 +4785,13 @@
         <v>19</v>
       </c>
       <c r="E105" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F105" s="19" t="s">
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H105" s="2">
         <v>10</v>
@@ -4818,16 +4818,16 @@
         <v>5</v>
       </c>
       <c r="D106" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E106" s="25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F106" s="19" t="s">
         <v>12</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H106" s="2">
         <v>14</v>
@@ -4856,7 +4856,7 @@
         <v>4</v>
       </c>
       <c r="D107" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E107" s="25" t="s">
         <v>18</v>
@@ -4865,7 +4865,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H107" s="2">
         <v>16</v>
@@ -4903,7 +4903,7 @@
         <v>11</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H108" s="2">
         <v>16</v>
@@ -4932,7 +4932,7 @@
         <v>4</v>
       </c>
       <c r="D109" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E109" s="25" t="s">
         <v>18</v>
@@ -4941,7 +4941,7 @@
         <v>16</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H109" s="2">
         <v>17</v>
@@ -4979,7 +4979,7 @@
         <v>11</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H110" s="2">
         <v>18</v>
@@ -5014,10 +5014,10 @@
         <v>11</v>
       </c>
       <c r="F111" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H111" s="2">
         <v>22</v>
@@ -5055,7 +5055,7 @@
         <v>17</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H112" s="2">
         <v>29</v>
@@ -5093,7 +5093,7 @@
         <v>12</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H113" s="2">
         <v>30</v>
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H114" s="2">
         <v>30</v>
@@ -5169,7 +5169,7 @@
         <v>19</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H115" s="2">
         <v>32</v>
@@ -5207,7 +5207,7 @@
         <v>17</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H116" s="2">
         <v>34</v>
@@ -5245,7 +5245,7 @@
         <v>17</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H117" s="2">
         <v>37</v>
@@ -5280,10 +5280,10 @@
         <v>18</v>
       </c>
       <c r="F118" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H118" s="2">
         <v>38</v>
@@ -5321,7 +5321,7 @@
         <v>9</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H119" s="2">
         <v>39</v>
@@ -5359,7 +5359,7 @@
         <v>11</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H120" s="2">
         <v>44</v>
@@ -5397,7 +5397,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H121" s="2">
         <v>44</v>
@@ -5432,10 +5432,10 @@
         <v>12</v>
       </c>
       <c r="F122" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H122" s="2">
         <v>45</v>
@@ -5473,7 +5473,7 @@
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H123" s="2">
         <v>46</v>
@@ -5511,7 +5511,7 @@
         <v>12</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H124" s="2">
         <v>48</v>
@@ -5549,7 +5549,7 @@
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H125" s="2">
         <v>49</v>
@@ -5587,7 +5587,7 @@
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H126" s="2">
         <v>52</v>
@@ -5616,7 +5616,7 @@
         <v>4</v>
       </c>
       <c r="D127" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E127" s="25" t="s">
         <v>12</v>
@@ -5625,7 +5625,7 @@
         <v>11</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H127" s="2">
         <v>54</v>
@@ -5663,7 +5663,7 @@
         <v>11</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H128" s="2">
         <v>5</v>
@@ -5699,7 +5699,7 @@
         <v>19</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H129" s="2">
         <v>11</v>
@@ -5737,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H130" s="2">
         <v>12</v>
@@ -5775,7 +5775,7 @@
         <v>9</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H131" s="2">
         <v>19</v>
@@ -5806,7 +5806,7 @@
         <v>5</v>
       </c>
       <c r="D132" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E132" s="25" t="s">
         <v>18</v>
@@ -5815,7 +5815,7 @@
         <v>9</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H132" s="2">
         <v>20</v>
@@ -5846,7 +5846,7 @@
         <v>5</v>
       </c>
       <c r="D133" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E133" s="25" t="s">
         <v>11</v>
@@ -5855,7 +5855,7 @@
         <v>19</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H133" s="2">
         <v>24</v>
@@ -5886,7 +5886,7 @@
         <v>4</v>
       </c>
       <c r="D134" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E134" s="25" t="s">
         <v>10</v>
@@ -5895,7 +5895,7 @@
         <v>18</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H134" s="2">
         <v>26</v>
@@ -5926,7 +5926,7 @@
         <v>4</v>
       </c>
       <c r="D135" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E135" s="25" t="s">
         <v>10</v>
@@ -5935,7 +5935,7 @@
         <v>8</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H135" s="2">
         <v>26</v>
@@ -5972,10 +5972,10 @@
         <v>11</v>
       </c>
       <c r="F136" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H136" s="2">
         <v>29</v>
@@ -6006,16 +6006,16 @@
         <v>5</v>
       </c>
       <c r="D137" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E137" s="25" t="s">
         <v>11</v>
       </c>
       <c r="F137" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H137" s="2">
         <v>30</v>
@@ -6055,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H138" s="2">
         <v>31</v>
@@ -6089,13 +6089,13 @@
         <v>8</v>
       </c>
       <c r="E139" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F139" s="19" t="s">
         <v>0</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H139" s="2">
         <v>37</v>
@@ -6135,7 +6135,7 @@
         <v>15</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H140" s="2">
         <v>39</v>
@@ -6166,16 +6166,16 @@
         <v>5</v>
       </c>
       <c r="D141" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E141" s="25" t="s">
         <v>18</v>
       </c>
       <c r="F141" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H141" s="2">
         <v>39</v>
@@ -6213,7 +6213,7 @@
         <v>11</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H142" s="2">
         <v>42</v>
@@ -6248,10 +6248,10 @@
         <v>18</v>
       </c>
       <c r="F143" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H143" s="2">
         <v>45</v>
@@ -6280,7 +6280,7 @@
         <v>5</v>
       </c>
       <c r="D144" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E144" s="25" t="s">
         <v>11</v>
@@ -6289,7 +6289,7 @@
         <v>10</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H144" s="2">
         <v>46</v>
@@ -6318,7 +6318,7 @@
         <v>5</v>
       </c>
       <c r="D145" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E145" s="25" t="s">
         <v>11</v>
@@ -6327,7 +6327,7 @@
         <v>19</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H145" s="2">
         <v>47</v>
@@ -6362,10 +6362,10 @@
         <v>10</v>
       </c>
       <c r="F146" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H146" s="2">
         <v>50</v>
@@ -6400,10 +6400,10 @@
         <v>10</v>
       </c>
       <c r="F147" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H147" s="2">
         <v>50</v>
@@ -6441,7 +6441,7 @@
         <v>10</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H148" s="2">
         <v>53</v>
@@ -6476,10 +6476,10 @@
         <v>12</v>
       </c>
       <c r="F149" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H149" s="2">
         <v>3</v>
@@ -6506,7 +6506,7 @@
         <v>5</v>
       </c>
       <c r="D150" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E150" s="25" t="s">
         <v>19</v>
@@ -6515,7 +6515,7 @@
         <v>8</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H150" s="2">
         <v>11</v>
@@ -6547,13 +6547,13 @@
         <v>8</v>
       </c>
       <c r="E151" s="25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F151" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H151" s="2">
         <v>16</v>
@@ -6591,7 +6591,7 @@
         <v>19</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H152" s="2">
         <v>21</v>
@@ -6629,7 +6629,7 @@
         <v>9</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H153" s="2">
         <v>23</v>
@@ -6658,16 +6658,16 @@
         <v>4</v>
       </c>
       <c r="D154" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E154" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F154" s="19" t="s">
         <v>0</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H154" s="2">
         <v>27</v>
@@ -6705,7 +6705,7 @@
         <v>18</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H155" s="2">
         <v>28</v>
@@ -6737,13 +6737,13 @@
         <v>19</v>
       </c>
       <c r="E156" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F156" s="19" t="s">
         <v>9</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H156" s="2">
         <v>28</v>
@@ -6781,7 +6781,7 @@
         <v>8</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H157" s="2">
         <v>29</v>
@@ -6819,7 +6819,7 @@
         <v>0</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H158" s="2">
         <v>30</v>
@@ -6854,10 +6854,10 @@
         <v>12</v>
       </c>
       <c r="F159" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H159" s="2">
         <v>34</v>
@@ -6895,7 +6895,7 @@
         <v>8</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H160" s="2">
         <v>36</v>
@@ -6933,7 +6933,7 @@
         <v>9</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H161" s="2">
         <v>38</v>
@@ -6962,16 +6962,16 @@
         <v>4</v>
       </c>
       <c r="D162" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E162" s="25" t="s">
         <v>18</v>
       </c>
       <c r="F162" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H162" s="2">
         <v>39</v>
@@ -7009,7 +7009,7 @@
         <v>16</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H163" s="2">
         <v>43</v>
@@ -7041,13 +7041,13 @@
         <v>12</v>
       </c>
       <c r="E164" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F164" s="19" t="s">
         <v>8</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H164" s="2">
         <v>47</v>
@@ -7085,7 +7085,7 @@
         <v>17</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H165" s="2">
         <v>50</v>
@@ -7123,7 +7123,7 @@
         <v>8</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H166" s="2">
         <v>57</v>
@@ -7161,7 +7161,7 @@
         <v>11</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H167" s="2">
         <v>7</v>
@@ -7197,7 +7197,7 @@
         <v>8</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H168" s="2">
         <v>10</v>
@@ -7235,7 +7235,7 @@
         <v>10</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H169" s="2">
         <v>13</v>
@@ -7264,7 +7264,7 @@
         <v>4</v>
       </c>
       <c r="D170" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E170" s="25" t="s">
         <v>11</v>
@@ -7273,7 +7273,7 @@
         <v>9</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H170" s="2">
         <v>21</v>
@@ -7305,13 +7305,13 @@
         <v>13</v>
       </c>
       <c r="E171" s="25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F171" s="19" t="s">
         <v>20</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H171" s="2">
         <v>21</v>
@@ -7349,7 +7349,7 @@
         <v>0</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H172" s="2">
         <v>22</v>
@@ -7378,7 +7378,7 @@
         <v>4</v>
       </c>
       <c r="D173" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E173" s="25" t="s">
         <v>11</v>
@@ -7387,7 +7387,7 @@
         <v>10</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H173" s="2">
         <v>26</v>
@@ -7422,10 +7422,10 @@
         <v>12</v>
       </c>
       <c r="F174" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H174" s="2">
         <v>33</v>
@@ -7463,7 +7463,7 @@
         <v>13</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H175" s="2">
         <v>34</v>
@@ -7501,7 +7501,7 @@
         <v>20</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H176" s="2">
         <v>38</v>
@@ -7539,7 +7539,7 @@
         <v>12</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H177" s="2">
         <v>45</v>
@@ -7571,13 +7571,13 @@
         <v>11</v>
       </c>
       <c r="E178" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F178" s="19" t="s">
         <v>12</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H178" s="2">
         <v>48</v>
@@ -7612,10 +7612,10 @@
         <v>11</v>
       </c>
       <c r="F179" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H179" s="2">
         <v>49</v>
@@ -7647,13 +7647,13 @@
         <v>19</v>
       </c>
       <c r="E180" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F180" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H180" s="2">
         <v>51</v>
@@ -7682,16 +7682,16 @@
         <v>4</v>
       </c>
       <c r="D181" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E181" s="25" t="s">
         <v>11</v>
       </c>
       <c r="F181" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H181" s="2">
         <v>53</v>
@@ -7729,7 +7729,7 @@
         <v>19</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H182" s="2">
         <v>54</v>
@@ -7764,10 +7764,10 @@
         <v>11</v>
       </c>
       <c r="F183" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H183" s="2">
         <v>55</v>
@@ -7802,10 +7802,10 @@
         <v>11</v>
       </c>
       <c r="F184" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H184" s="2">
         <v>5</v>
@@ -7841,7 +7841,7 @@
         <v>19</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H185" s="2">
         <v>7</v>
@@ -7879,7 +7879,7 @@
         <v>0</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H186" s="2">
         <v>26</v>
@@ -7917,7 +7917,7 @@
         <v>10</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H187" s="2">
         <v>27</v>
@@ -7955,7 +7955,7 @@
         <v>13</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H188" s="2">
         <v>28</v>
@@ -7993,7 +7993,7 @@
         <v>11</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H189" s="2">
         <v>35</v>
@@ -8025,13 +8025,13 @@
         <v>11</v>
       </c>
       <c r="E190" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F190" s="19" t="s">
         <v>19</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H190" s="2">
         <v>36</v>
@@ -8069,7 +8069,7 @@
         <v>15</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H191" s="2">
         <v>37</v>
@@ -8107,7 +8107,7 @@
         <v>19</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H192" s="2">
         <v>40</v>
@@ -8145,7 +8145,7 @@
         <v>0</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H193" s="2">
         <v>46</v>
@@ -8183,7 +8183,7 @@
         <v>9</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H194" s="2">
         <v>48</v>
@@ -8221,7 +8221,7 @@
         <v>12</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H195" s="2">
         <v>51</v>
@@ -8259,7 +8259,7 @@
         <v>11</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H196" s="2">
         <v>53</v>
@@ -8297,7 +8297,7 @@
         <v>0</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H197" s="2">
         <v>54</v>
@@ -8326,7 +8326,7 @@
         <v>5</v>
       </c>
       <c r="D198" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E198" s="25" t="s">
         <v>11</v>
@@ -8335,7 +8335,7 @@
         <v>0</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H198" s="2">
         <v>55</v>
@@ -8373,7 +8373,7 @@
         <v>18</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H199" s="2">
         <v>4</v>
@@ -8409,7 +8409,7 @@
         <v>0</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H200" s="2">
         <v>9</v>
@@ -8438,7 +8438,7 @@
         <v>4</v>
       </c>
       <c r="D201" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E201" s="25" t="s">
         <v>11</v>
@@ -8447,7 +8447,7 @@
         <v>19</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H201" s="2">
         <v>14</v>
@@ -8485,7 +8485,7 @@
         <v>8</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H202" s="2">
         <v>15</v>
@@ -8514,16 +8514,16 @@
         <v>5</v>
       </c>
       <c r="D203" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E203" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F203" s="19" t="s">
         <v>0</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H203" s="2">
         <v>18</v>
@@ -8561,7 +8561,7 @@
         <v>11</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H204" s="2">
         <v>20</v>
@@ -8599,7 +8599,7 @@
         <v>13</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H205" s="2">
         <v>22</v>
@@ -8628,7 +8628,7 @@
         <v>4</v>
       </c>
       <c r="D206" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E206" s="25" t="s">
         <v>11</v>
@@ -8637,7 +8637,7 @@
         <v>19</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H206" s="2">
         <v>26</v>
@@ -8669,13 +8669,13 @@
         <v>9</v>
       </c>
       <c r="E207" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F207" s="19" t="s">
         <v>0</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H207" s="2">
         <v>27</v>
@@ -8707,13 +8707,13 @@
         <v>19</v>
       </c>
       <c r="E208" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F208" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H208" s="2">
         <v>27</v>
@@ -8742,16 +8742,16 @@
         <v>4</v>
       </c>
       <c r="D209" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E209" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F209" s="19" t="s">
         <v>0</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H209" s="2">
         <v>28</v>
@@ -8783,13 +8783,13 @@
         <v>18</v>
       </c>
       <c r="E210" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F210" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H210" s="2">
         <v>33</v>
@@ -8827,7 +8827,7 @@
         <v>10</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H211" s="2">
         <v>33</v>
@@ -8859,13 +8859,13 @@
         <v>11</v>
       </c>
       <c r="E212" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F212" s="19" t="s">
         <v>8</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H212" s="2">
         <v>34</v>
@@ -8897,13 +8897,13 @@
         <v>13</v>
       </c>
       <c r="E213" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F213" s="19" t="s">
         <v>0</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H213" s="2">
         <v>36</v>
@@ -8932,7 +8932,7 @@
         <v>4</v>
       </c>
       <c r="D214" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E214" s="25" t="s">
         <v>12</v>
@@ -8941,7 +8941,7 @@
         <v>9</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H214" s="2">
         <v>39</v>
@@ -8976,10 +8976,10 @@
         <v>13</v>
       </c>
       <c r="F215" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H215" s="2">
         <v>42</v>
@@ -9014,10 +9014,10 @@
         <v>8</v>
       </c>
       <c r="F216" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H216" s="2">
         <v>47</v>
@@ -9055,7 +9055,7 @@
         <v>16</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H217" s="2">
         <v>53</v>
@@ -9087,13 +9087,13 @@
         <v>13</v>
       </c>
       <c r="E218" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F218" s="19" t="s">
         <v>8</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H218" s="2">
         <v>53</v>
@@ -9125,13 +9125,13 @@
         <v>12</v>
       </c>
       <c r="E219" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F219" s="19" t="s">
         <v>13</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H219" s="2">
         <v>54</v>
@@ -9169,7 +9169,7 @@
         <v>0</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H220" s="2">
         <v>57</v>
@@ -9207,7 +9207,7 @@
         <v>9</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H221" s="2">
         <v>58</v>
@@ -9245,7 +9245,7 @@
         <v>0</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H222" s="2">
         <v>8</v>
@@ -9275,13 +9275,13 @@
         <v>11</v>
       </c>
       <c r="E223" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F223" s="19" t="s">
         <v>0</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H223" s="2">
         <v>14</v>
@@ -9316,10 +9316,10 @@
         <v>18</v>
       </c>
       <c r="F224" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H224" s="2">
         <v>18</v>
@@ -9354,10 +9354,10 @@
         <v>20</v>
       </c>
       <c r="F225" s="19" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H225" s="2">
         <v>19</v>
@@ -9389,13 +9389,13 @@
         <v>11</v>
       </c>
       <c r="E226" s="25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F226" s="19" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H226" s="2">
         <v>21</v>
@@ -9424,7 +9424,7 @@
         <v>4</v>
       </c>
       <c r="D227" s="19" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="E227" s="25" t="s">
         <v>13</v>
@@ -9433,7 +9433,7 @@
         <v>19</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H227" s="2">
         <v>36</v>
@@ -9468,10 +9468,10 @@
         <v>13</v>
       </c>
       <c r="F228" s="19" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H228" s="2">
         <v>38</v>
@@ -9509,7 +9509,7 @@
         <v>19</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H229" s="2">
         <v>40</v>
@@ -9544,10 +9544,10 @@
         <v>11</v>
       </c>
       <c r="F230" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H230" s="2">
         <v>42</v>
@@ -9585,7 +9585,7 @@
         <v>0</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H231" s="2">
         <v>45</v>
@@ -9623,7 +9623,7 @@
         <v>0</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H232" s="2">
         <v>50</v>
@@ -9661,7 +9661,7 @@
         <v>11</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H233" s="2">
         <v>56</v>
@@ -9690,7 +9690,7 @@
         <v>5</v>
       </c>
       <c r="D234" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E234" s="25" t="s">
         <v>11</v>
@@ -9699,7 +9699,7 @@
         <v>18</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H234" s="2">
         <v>4</v>
@@ -9732,10 +9732,10 @@
         <v>18</v>
       </c>
       <c r="F235" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H235" s="2">
         <v>10</v>
@@ -9770,10 +9770,10 @@
         <v>11</v>
       </c>
       <c r="F236" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H236" s="2">
         <v>14</v>
@@ -9808,10 +9808,10 @@
         <v>11</v>
       </c>
       <c r="F237" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H237" s="2">
         <v>25</v>
@@ -9843,13 +9843,13 @@
         <v>10</v>
       </c>
       <c r="E238" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F238" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H238" s="2">
         <v>29</v>
@@ -9881,13 +9881,13 @@
         <v>19</v>
       </c>
       <c r="E239" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F239" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H239" s="2">
         <v>44</v>
@@ -9925,7 +9925,7 @@
         <v>13</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H240" s="2">
         <v>46</v>
@@ -9963,7 +9963,7 @@
         <v>0</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H241" s="2">
         <v>55</v>
@@ -10001,7 +10001,7 @@
         <v>0</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H242" s="2">
         <v>57</v>
@@ -10033,13 +10033,13 @@
         <v>13</v>
       </c>
       <c r="E243" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F243" s="19" t="s">
         <v>0</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H243" s="2">
         <v>59</v>
@@ -10077,7 +10077,7 @@
         <v>0</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H244" s="2">
         <v>2</v>
@@ -10113,7 +10113,7 @@
         <v>13</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H245" s="2">
         <v>2</v>
@@ -10145,13 +10145,13 @@
         <v>20</v>
       </c>
       <c r="E246" s="25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F246" s="19" t="s">
         <v>0</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H246" s="2">
         <v>4</v>
@@ -10183,13 +10183,13 @@
         <v>12</v>
       </c>
       <c r="E247" s="25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F247" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H247" s="2">
         <v>5</v>
@@ -10218,16 +10218,16 @@
         <v>5</v>
       </c>
       <c r="D248" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E248" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F248" s="19" t="s">
         <v>0</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H248" s="2">
         <v>16</v>
@@ -10256,7 +10256,7 @@
         <v>4</v>
       </c>
       <c r="D249" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E249" s="25" t="s">
         <v>13</v>
@@ -10265,7 +10265,7 @@
         <v>9</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H249" s="2">
         <v>23</v>
@@ -10303,7 +10303,7 @@
         <v>19</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H250" s="2">
         <v>39</v>
@@ -10335,13 +10335,13 @@
         <v>10</v>
       </c>
       <c r="E251" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F251" s="19" t="s">
         <v>13</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H251" s="2">
         <v>42</v>
@@ -10373,13 +10373,13 @@
         <v>13</v>
       </c>
       <c r="E252" s="25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F252" s="19" t="s">
         <v>20</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H252" s="2">
         <v>50</v>
@@ -10411,13 +10411,13 @@
         <v>13</v>
       </c>
       <c r="E253" s="25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F253" s="19" t="s">
         <v>10</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H253" s="2">
         <v>51</v>
@@ -10449,13 +10449,13 @@
         <v>20</v>
       </c>
       <c r="E254" s="25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F254" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H254" s="2">
         <v>53</v>
@@ -10487,13 +10487,13 @@
         <v>13</v>
       </c>
       <c r="E255" s="25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F255" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H255" s="2">
         <v>54</v>
@@ -10522,7 +10522,7 @@
         <v>4</v>
       </c>
       <c r="D256" s="23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E256" s="29" t="s">
         <v>8</v>
@@ -10531,7 +10531,7 @@
         <v>9</v>
       </c>
       <c r="G256" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H256" s="8">
         <v>56</v>
